--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Vente de murs libres de local commercial situé sur la ville de Bondy d'une surface de 188m² de plain pied. Le local est livré brut de béton avc fluides en attente et vitrines à poser par le preneur. Le local se situe dans un quartier en pleine rénovation , avec de nombreuses résidences et commerces en pied d'immeuble. Le local se situe à deux pas de la future nouvelle gare Pont de Bondy de la ligne 15 Est. L'accès au local est aisé par la future gare Pont de Bondy, les rocades de la A 3 et A86, nombreux bus. Réf AAL 841200</t>
+          <t>Vente de murs libres de local commercial situé sur la ville de Bondy d'une surface de 188m² de plain pied. Le local est livré brut de béton avc fluides en attente et vitrines à poser par le preneur. Le local se situe dans un quartier en pleine rénovation , avec de nombreuses résidences et commerces en pied d'immeuble. Le local se situe à deux pas de la future nouvelle gare Pont de Bondy de la ligne 15 Est. L'accès au local est aisé par la future gare Pont de Bondy, les rocades de la A 3 et A86, nombreux bus. Livraison second semestre 2028 Réf AAL 841200</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +356 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +458 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +458 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +356 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +356 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +330 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +330 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +307 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-bondy-42364e9d.xlsx
+++ b/docs/dossiers/dossier-bondy-42364e9d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
